--- a/Project/DiceWarrior/LubanTool/Datas/奖励表.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/奖励表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="17470"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -47,7 +47,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
+    <t>(list#sep=|),int</t>
   </si>
   <si>
     <t>##group</t>
@@ -56,10 +56,25 @@
     <t>##</t>
   </si>
   <si>
-    <t>1 1 2</t>
+    <t>ID</t>
   </si>
   <si>
-    <t>1 2 2</t>
+    <t>稀有度</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>1|1|2</t>
+  </si>
+  <si>
+    <t>1|2|2</t>
+  </si>
+  <si>
+    <t>1|2|3</t>
+  </si>
+  <si>
+    <t>2|3|3</t>
   </si>
 </sst>
 </file>
@@ -72,10 +87,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -225,7 +248,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,6 +257,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -419,11 +460,115 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -545,139 +690,172 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1204,111 +1382,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="8.54545454545454" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.4545454545455" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.9090909090909" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.2727272727273" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.72727272727273" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" ht="25" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:5">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:5">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:5">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6">
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="9">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7">
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" ht="25" customHeight="1" spans="1:5">
+      <c r="A7" s="6"/>
+      <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" ht="25" customHeight="1" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9">
         <v>1001</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="9">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9">
+      <c r="D8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:5">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7">
         <v>1002</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10">
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" ht="25" customHeight="1" spans="1:5">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9">
         <v>1003</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="9">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11">
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" ht="25" customHeight="1" spans="1:5">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7">
         <v>1004</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>4</v>
       </c>
+      <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" ht="25" customHeight="1" spans="1:5">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:5">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:5">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:5">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" ht="25" customHeight="1" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" ht="25" customHeight="1" spans="1:5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" ht="25" customHeight="1" spans="1:5">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Project/DiceWarrior/LubanTool/Datas/奖励表.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/奖励表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\ProjectDiceWarrior\Project\DiceWarrior\LubanTool\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17470"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -75,6 +80,156 @@
   </si>
   <si>
     <t>2|3|3</t>
+  </si>
+  <si>
+    <t>10001|10002</t>
+  </si>
+  <si>
+    <t>10003|10004|10005</t>
+  </si>
+  <si>
+    <t>10005|10006</t>
+  </si>
+  <si>
+    <t>10007|10008|10009</t>
+  </si>
+  <si>
+    <t>10009|10010</t>
+  </si>
+  <si>
+    <t>10011|10012|10013</t>
+  </si>
+  <si>
+    <t>10013|10014</t>
+  </si>
+  <si>
+    <t>10015|10016|10017</t>
+  </si>
+  <si>
+    <t>10017|10018</t>
+  </si>
+  <si>
+    <t>10019|10020|10021</t>
+  </si>
+  <si>
+    <t>10021|10022</t>
+  </si>
+  <si>
+    <t>10023|10024|10025</t>
+  </si>
+  <si>
+    <t>10025|10026</t>
+  </si>
+  <si>
+    <t>10027|10028|10029</t>
+  </si>
+  <si>
+    <t>10029|10030</t>
+  </si>
+  <si>
+    <t>10031|10032|10033</t>
+  </si>
+  <si>
+    <t>10033|10034</t>
+  </si>
+  <si>
+    <t>10035|10036|10037</t>
+  </si>
+  <si>
+    <t>10037|10038</t>
+  </si>
+  <si>
+    <t>10039|10040|10041</t>
+  </si>
+  <si>
+    <t>10041|10042</t>
+  </si>
+  <si>
+    <t>10043|10044|10045</t>
+  </si>
+  <si>
+    <t>10045|10046</t>
+  </si>
+  <si>
+    <t>10047|10048|10049</t>
+  </si>
+  <si>
+    <t>10049|10050</t>
+  </si>
+  <si>
+    <t>10051|10052|10053</t>
+  </si>
+  <si>
+    <t>10053|10054</t>
+  </si>
+  <si>
+    <t>10055|10056|10057</t>
+  </si>
+  <si>
+    <t>10057|10058</t>
+  </si>
+  <si>
+    <t>10059|10060|10061</t>
+  </si>
+  <si>
+    <t>10061|10062</t>
+  </si>
+  <si>
+    <t>10063|10064|10065</t>
+  </si>
+  <si>
+    <t>10065|10066</t>
+  </si>
+  <si>
+    <t>10067|10068|10069</t>
+  </si>
+  <si>
+    <t>10069|10070</t>
+  </si>
+  <si>
+    <t>10071|10072|10073</t>
+  </si>
+  <si>
+    <t>10073|10074</t>
+  </si>
+  <si>
+    <t>10075|10076|10077</t>
+  </si>
+  <si>
+    <t>10077|10078</t>
+  </si>
+  <si>
+    <t>10079|10080|10081</t>
+  </si>
+  <si>
+    <t>10081|10082</t>
+  </si>
+  <si>
+    <t>10083|10084|10085</t>
+  </si>
+  <si>
+    <t>10085|10086</t>
+  </si>
+  <si>
+    <t>10087|10088|10089</t>
+  </si>
+  <si>
+    <t>10089|10090</t>
+  </si>
+  <si>
+    <t>10091|10092|10093</t>
+  </si>
+  <si>
+    <t>10093|10094</t>
+  </si>
+  <si>
+    <t>10095|10096|10097</t>
+  </si>
+  <si>
+    <t>10097|10098</t>
+  </si>
+  <si>
+    <t>10099|10100|10001</t>
   </si>
 </sst>
 </file>
@@ -87,13 +242,12 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -101,30 +255,24 @@
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -132,15 +280,13 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -148,7 +294,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -156,7 +301,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -164,88 +308,70 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -323,19 +449,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,19 +473,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,19 +497,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,19 +521,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,19 +545,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -443,24 +569,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -493,29 +619,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thick">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thick">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
+      <right/>
+      <top/>
+      <bottom style="thick">
         <color theme="0"/>
       </bottom>
       <diagonal/>
@@ -525,7 +634,7 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
+      <top style="thick">
         <color theme="0"/>
       </top>
       <bottom style="thin">
@@ -540,7 +649,20 @@
       <right style="thin">
         <color theme="0"/>
       </right>
-      <top style="thin">
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
         <color theme="0"/>
       </top>
       <bottom style="thin">
@@ -556,6 +678,47 @@
       <top style="thin">
         <color theme="0"/>
       </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -566,6 +729,17 @@
       <right style="thin">
         <color theme="0"/>
       </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
       <top style="thin">
         <color theme="0"/>
       </top>
@@ -601,7 +775,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -696,7 +870,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -708,34 +882,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -750,10 +924,10 @@
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -762,10 +936,10 @@
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -774,10 +948,10 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -786,10 +960,10 @@
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -798,10 +972,10 @@
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -810,17 +984,17 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,18 +1007,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -855,6 +1023,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,76 +1380,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -1266,9 +1413,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -1278,27 +1423,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -1307,7 +1448,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1350,17 +1490,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1382,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.54545454545454" style="1" customWidth="1"/>
@@ -1406,192 +1546,786 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="12">
         <v>1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:5">
-      <c r="A7" s="6"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="9">
         <v>1</v>
       </c>
-      <c r="D7" s="7">
-        <v>2</v>
-      </c>
-      <c r="E7" s="7"/>
+      <c r="D7" s="9">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:5">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12">
         <v>1001</v>
       </c>
-      <c r="C8" s="9">
-        <v>2</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="12">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="13"/>
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:5">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
         <v>1002</v>
       </c>
-      <c r="C9" s="7">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:5">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12">
         <v>1003</v>
       </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="12">
+        <v>3</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9">
         <v>1004</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <v>4</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="12">
+        <v>2001</v>
+      </c>
+      <c r="C12" s="12">
+        <v>2</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:5">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9">
+        <v>2002</v>
+      </c>
+      <c r="C13" s="9">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:5">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="12">
+        <v>2003</v>
+      </c>
+      <c r="C14" s="12">
+        <v>2</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:5">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9">
+        <v>2004</v>
+      </c>
+      <c r="C15" s="9">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="12">
+        <v>2005</v>
+      </c>
+      <c r="C16" s="12">
+        <v>2</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9">
+        <v>2006</v>
+      </c>
+      <c r="C17" s="9">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="12">
+        <v>2007</v>
+      </c>
+      <c r="C18" s="12">
+        <v>2</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="13"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:5">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9">
+        <v>2008</v>
+      </c>
+      <c r="C19" s="9">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="14"/>
+      <c r="B20" s="15">
+        <v>2009</v>
+      </c>
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18">
+        <v>2010</v>
+      </c>
+      <c r="C21" s="18">
+        <v>3</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="14"/>
+      <c r="B22" s="15">
+        <v>2011</v>
+      </c>
+      <c r="C22" s="15">
+        <v>2</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18">
+        <v>2012</v>
+      </c>
+      <c r="C23" s="18">
+        <v>3</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="14"/>
+      <c r="B24" s="15">
+        <v>2013</v>
+      </c>
+      <c r="C24" s="15">
+        <v>2</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18">
+        <v>2014</v>
+      </c>
+      <c r="C25" s="18">
+        <v>3</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="14"/>
+      <c r="B26" s="15">
+        <v>2015</v>
+      </c>
+      <c r="C26" s="15">
+        <v>2</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18">
+        <v>2016</v>
+      </c>
+      <c r="C27" s="18">
+        <v>3</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="14"/>
+      <c r="B28" s="15">
+        <v>2017</v>
+      </c>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18">
+        <v>2018</v>
+      </c>
+      <c r="C29" s="18">
+        <v>3</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="14"/>
+      <c r="B30" s="15">
+        <v>2019</v>
+      </c>
+      <c r="C30" s="15">
+        <v>2</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18">
+        <v>2020</v>
+      </c>
+      <c r="C31" s="18">
+        <v>3</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="14"/>
+      <c r="B32" s="15">
+        <v>2021</v>
+      </c>
+      <c r="C32" s="15">
+        <v>2</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18">
+        <v>2022</v>
+      </c>
+      <c r="C33" s="18">
+        <v>3</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="14"/>
+      <c r="B34" s="15">
+        <v>2023</v>
+      </c>
+      <c r="C34" s="15">
+        <v>2</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="16"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18">
+        <v>2024</v>
+      </c>
+      <c r="C35" s="18">
+        <v>3</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15">
+        <v>2025</v>
+      </c>
+      <c r="C36" s="15">
+        <v>2</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C37" s="18">
+        <v>3</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15">
+        <v>2027</v>
+      </c>
+      <c r="C38" s="15">
+        <v>2</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18">
+        <v>2028</v>
+      </c>
+      <c r="C39" s="18">
+        <v>3</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="14"/>
+      <c r="B40" s="15">
+        <v>2029</v>
+      </c>
+      <c r="C40" s="15">
+        <v>2</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="17"/>
+      <c r="B41" s="18">
+        <v>2030</v>
+      </c>
+      <c r="C41" s="18">
+        <v>3</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="14"/>
+      <c r="B42" s="15">
+        <v>2031</v>
+      </c>
+      <c r="C42" s="15">
+        <v>2</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="17"/>
+      <c r="B43" s="18">
+        <v>2032</v>
+      </c>
+      <c r="C43" s="18">
+        <v>3</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="14"/>
+      <c r="B44" s="15">
+        <v>2033</v>
+      </c>
+      <c r="C44" s="15">
+        <v>2</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="17"/>
+      <c r="B45" s="18">
+        <v>2034</v>
+      </c>
+      <c r="C45" s="18">
+        <v>3</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="14"/>
+      <c r="B46" s="15">
+        <v>2035</v>
+      </c>
+      <c r="C46" s="15">
+        <v>2</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="17"/>
+      <c r="B47" s="18">
+        <v>2036</v>
+      </c>
+      <c r="C47" s="18">
+        <v>3</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15">
+        <v>2037</v>
+      </c>
+      <c r="C48" s="15">
+        <v>2</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="16"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="17"/>
+      <c r="B49" s="18">
+        <v>2038</v>
+      </c>
+      <c r="C49" s="18">
+        <v>3</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15">
+        <v>2039</v>
+      </c>
+      <c r="C50" s="15">
+        <v>2</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="16"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="17"/>
+      <c r="B51" s="18">
+        <v>2040</v>
+      </c>
+      <c r="C51" s="18">
+        <v>3</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15">
+        <v>2041</v>
+      </c>
+      <c r="C52" s="15">
+        <v>2</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" s="16"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="17"/>
+      <c r="B53" s="18">
+        <v>2042</v>
+      </c>
+      <c r="C53" s="18">
+        <v>3</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15">
+        <v>2043</v>
+      </c>
+      <c r="C54" s="15">
+        <v>2</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="16"/>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="17"/>
+      <c r="B55" s="18">
+        <v>2044</v>
+      </c>
+      <c r="C55" s="18">
+        <v>3</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="14"/>
+      <c r="B56" s="15">
+        <v>2045</v>
+      </c>
+      <c r="C56" s="15">
+        <v>2</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="16"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="17"/>
+      <c r="B57" s="18">
+        <v>2046</v>
+      </c>
+      <c r="C57" s="18">
+        <v>3</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="14"/>
+      <c r="B58" s="15">
+        <v>2047</v>
+      </c>
+      <c r="C58" s="15">
+        <v>2</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" s="16"/>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="17"/>
+      <c r="B59" s="18">
+        <v>2048</v>
+      </c>
+      <c r="C59" s="18">
+        <v>3</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="14"/>
+      <c r="B60" s="15">
+        <v>2049</v>
+      </c>
+      <c r="C60" s="15">
+        <v>2</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E60" s="16"/>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="20"/>
+      <c r="B61" s="21">
+        <v>2050</v>
+      </c>
+      <c r="C61" s="21">
+        <v>3</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" s="22"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>